--- a/Data_preprocessing/src/Hybridization/mappings/NGFS_energy_uses.xlsx
+++ b/Data_preprocessing/src/Hybridization/mappings/NGFS_energy_uses.xlsx
@@ -19,32 +19,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">CAVEAT: we ignore systematically the production and use of biomass.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t xml:space="preserve">NGFS_volume</t>
   </si>
@@ -55,7 +31,7 @@
     <t xml:space="preserve">energy_use</t>
   </si>
   <si>
-    <t xml:space="preserve">Primary Energy|Coal|Electricity</t>
+    <t xml:space="preserve">PE|Coal|+|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Primary Energy|Coal</t>
@@ -64,73 +40,73 @@
     <t xml:space="preserve">PE</t>
   </si>
   <si>
-    <t xml:space="preserve">Primary Energy|Coal|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Energy|Coal|Heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Energy|Coal|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Energy|Gas|Electricity</t>
+    <t xml:space="preserve">PE|Coal|+|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE|Coal|+|Heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE|Coal|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE|Gas|+|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Primary Energy|Gas</t>
   </si>
   <si>
-    <t xml:space="preserve">Primary Energy|Gas|Heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Energy|Gas|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Energy|Oil</t>
+    <t xml:space="preserve">PE|Gas|+|Heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE|Gas|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE|+|Oil</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Primary Energy|Oil</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Residential and Commercial|Electricity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Residential and Commercial|Residential|Electricity</t>
+    <t xml:space="preserve">FE|Buildings|+|Electricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Buildings|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">R&amp;C</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Residential and Commercial|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Residential and Commercial|Residential|Gases|Natural Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Residential and Commercial|Heat</t>
+    <t xml:space="preserve">FE|Buildings|+|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Buildings|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Buildings|+|Heat</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Buildings|Heat</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Residential and Commercial|Hydrogen</t>
+    <t xml:space="preserve">FE|Buildings|+|Hydrogen</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Buildings|Hydrogen</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Residential and Commercial|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Residential and Commercial|Residential|Liquids|Oil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Residential and Commercial|Solids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Residential and Commercial|Residential|Solids|Coal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Steel|Electricity</t>
+    <t xml:space="preserve">FE|Buildings|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Buildings|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Buildings|+|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Buildings|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Steel|+|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Industry|Electricity</t>
@@ -139,127 +115,115 @@
     <t xml:space="preserve">ST</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Industry|Chemicals|Electricity</t>
+    <t xml:space="preserve">FE|Industry|Chemicals|+|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">CH</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Industry|Cement|Electricity</t>
+    <t xml:space="preserve">FE|Industry|Cement|+|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">IND</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Industry|Other|Electricity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Steel|Gases</t>
+    <t xml:space="preserve">FE|Industry|Other Industry|+|Electricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Steel|+|Gases</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Industry|Gases</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Industry|Chemicals|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Cement|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Other|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Steel|Hydrogen</t>
+    <t xml:space="preserve">FE|Industry|Chemicals|+|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Cement|+|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Other Industry|+|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Steel|+|Hydrogen</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Industry|Hydrogen</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Industry|Chemicals|Hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Cement|Hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Other|Hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Steel|Liquids</t>
+    <t xml:space="preserve">FE|Industry|Chemicals|+|Hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Cement|+|Hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Other Industry|+|Hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Steel|+|Liquids</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Industry|Liquids</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Industry|Chemicals|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Cement|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Other|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Steel|Solids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Industry|Solids|Coal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Chemicals|Solids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Cement|Solids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Other|Solids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Industry|Other|Heat</t>
+    <t xml:space="preserve">FE|Industry|Chemicals|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Cement|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Other Industry|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Steel|+|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Industry|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Chemicals|+|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Cement|+|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|Other Industry|+|Solids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Industry|+|Heat</t>
   </si>
   <si>
     <t xml:space="preserve">Price|Final Energy|Industry|Heat</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Transportation|Freight|Electricity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Transportation|Electricity</t>
+    <t xml:space="preserve">FE|Transport|+|Electricity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Transport|Electricity</t>
   </si>
   <si>
     <t xml:space="preserve">FRE</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Energy|Transportation|Freight|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Transportation|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Transportation|Freight|Hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Transportation|Hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Transportation|Freight|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price|Final Energy|Transportation|Liquids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Transportation|Passenger|Electricity</t>
+    <t xml:space="preserve">FE|Transport|+|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Transport|Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Transport|+|Hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Transport|Hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE|Transport|+|Liquids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price|Final Energy|Transport|Liquids</t>
   </si>
   <si>
     <t xml:space="preserve">PAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Transportation|Passenger|Gases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Transportation|Passenger|Hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Energy|Transportation|Passenger|Liquids</t>
   </si>
 </sst>
 </file>
@@ -269,7 +233,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -291,14 +255,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,7 +306,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -359,28 +315,16 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -400,16 +344,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1048576"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="57.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="80.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1023" style="0" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -420,7 +365,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="0" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -431,477 +376,467 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="C18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="C19" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="C22" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="C30" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="C31" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="C34" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
+      <c r="C36" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="4" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="4" t="s">
+      <c r="C42" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="4" t="s">
+      <c r="C43" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C44" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -910,6 +845,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>